--- a/AAII_Financials/Quarterly/BKZHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKZHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>BKZHY</t>
   </si>
@@ -656,66 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -746,8 +750,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -778,8 +785,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -810,8 +820,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +837,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,8 +870,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,8 +905,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -920,8 +940,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -952,8 +975,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,8 +989,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -995,8 +1022,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1027,8 +1057,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1041,8 +1074,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1073,8 +1107,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1105,8 +1142,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1137,8 +1177,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1169,8 +1212,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1201,8 +1247,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1233,8 +1282,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1265,8 +1317,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1297,8 +1352,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1329,8 +1387,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1422,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1393,8 +1457,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1425,8 +1492,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1457,8 +1527,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1489,8 +1562,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1521,8 +1597,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1553,45 +1632,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1604,8 +1689,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1618,72 +1704,79 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1692200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1304700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1070300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5831100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1747400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>347700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1328400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1305900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2302400</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7474600</v>
+      </c>
+      <c r="E42" s="3">
         <v>5707900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7148000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7011800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3660700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5534900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5453700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4847400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4577100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5898800</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1699,23 +1792,26 @@
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>591800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1731,11 +1827,11 @@
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -1743,11 +1839,14 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1755,159 +1854,174 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>7696800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7601500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12810900</v>
+      </c>
+      <c r="E46" s="3">
         <v>10100000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19907900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18383100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11389700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10227500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8827200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7948900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7823100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10030200</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22489900</v>
+      </c>
+      <c r="E47" s="3">
         <v>23082500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20255200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20882300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20106600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17392800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>17289600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16055100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16629700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15832200</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>327200</v>
+      </c>
+      <c r="E48" s="3">
         <v>341900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>337200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>306300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>323800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>310700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>331300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>322600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>319000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>719900</v>
+      </c>
+      <c r="E49" s="3">
         <v>717800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>698700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>701500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>686500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>651300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>678500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>642300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>646000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>659800</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1938,8 +2052,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1970,40 +2087,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3243600</v>
+      </c>
+      <c r="E52" s="3">
         <v>2076200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1416300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1597200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1790300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>299900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1623300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1675800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1286200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>80300</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2034,40 +2157,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>85730200</v>
+      </c>
+      <c r="E54" s="3">
         <v>81705400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87287900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87086600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80982200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>73644800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75730500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70357300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70343900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70368000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2080,8 +2209,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2094,200 +2224,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65688400</v>
+      </c>
+      <c r="E57" s="3">
         <v>61551900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>61373100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61736100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>61618100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56589700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57254100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54026100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53353400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53696100</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5983600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4332400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4314500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4322200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3277300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3045200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3118700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3297800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2990600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2580600</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>919700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1044300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7128500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6996200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>463100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>750200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>752700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>567400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>493600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>839400</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72847400</v>
+      </c>
+      <c r="E60" s="3">
         <v>67142700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72987600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73214300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65596500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60624400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61408500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58123600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57028700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>57360900</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2991200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3497100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3228900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3264500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4616900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3710700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4476500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3355800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3330100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3507000</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1257600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1396000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1193000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1279800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1254500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>906400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>941200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1052100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1060100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>862500</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,8 +2467,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,8 +2502,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2382,40 +2537,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77158400</v>
+      </c>
+      <c r="E66" s="3">
         <v>72098400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77564700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77894100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71544800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65311600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66898900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62598700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61547900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61798500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2428,8 +2589,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2460,8 +2622,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2492,8 +2657,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2524,8 +2692,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2556,40 +2727,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1833900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2956100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2134800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1626500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2310400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5903600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1665700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1108300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1886100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6032000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2620,8 +2797,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2652,8 +2832,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,40 +2867,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9579700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9156500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8645200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8926200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7870200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8330200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7297600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8303900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8079000</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2748,45 +2937,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2817,8 +3012,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,40 +3029,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E83" s="3">
         <v>37700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>38100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2895,8 +3097,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2927,8 +3132,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2959,8 +3167,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2991,8 +3202,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3023,40 +3237,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-518600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>274900</v>
       </c>
-      <c r="F89" s="3">
-        <v>4487800</v>
-      </c>
       <c r="G89" s="3">
+        <v>4401500</v>
+      </c>
+      <c r="H89" s="3">
         <v>418100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1453500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1738100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1451000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-586600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-641600</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3069,40 +3289,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3133,8 +3357,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3165,40 +3392,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-226000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1375800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>690500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-526200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1326000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1095600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>271900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>342600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-981800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-778200</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3211,40 +3444,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>1357400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>1311900</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>1134300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>604300</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3275,8 +3512,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3307,8 +3547,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3339,40 +3582,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2556500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1041200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>199200</v>
       </c>
-      <c r="F100" s="3">
-        <v>-6291200</v>
-      </c>
       <c r="G100" s="3">
+        <v>-6204900</v>
+      </c>
+      <c r="H100" s="3">
         <v>1149800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3695300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1089100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>204000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>256200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-305300</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3403,36 +3652,42 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1811900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2419100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1164600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2329600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>241900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1146300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-377200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-904400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1312300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1725200</v>
       </c>
     </row>
